--- a/data/trans_orig/IP3109_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Provincia-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>29263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36664</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58879</t>
+          <t>58936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87262</t>
+          <t>86059</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112040</t>
+          <t>112023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68676</t>
+          <t>68716</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102240</t>
+          <t>103776</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61120</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99946</t>
+          <t>105241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43572</t>
+          <t>43196</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67138</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113714</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174910</t>
+          <t>170383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26693</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>39640</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>29093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42707</t>
+          <t>42888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61468</t>
+          <t>61274</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78409</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>539</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>57642</t>
+          <t>57821</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66163</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62301</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>72753</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>124520</t>
+          <t>124174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>137346</t>
+          <t>137421</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22262</t>
+          <t>22216</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53968</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24372</t>
+          <t>23853</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>40602</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>100300</t>
+          <t>100278</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>108766</t>
+          <t>108527</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>128141</t>
+          <t>128512</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>197193</t>
+          <t>198819</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>223519</t>
+          <t>225253</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>951</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>62765</t>
+          <t>61272</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>86679</t>
+          <t>86142</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>105273</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>115706</t>
+          <t>115454</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>132474</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>206550</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>232229</t>
+          <t>232568</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>126295</t>
+          <t>126640</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>168418</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>102273</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>140992</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>127036</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>174211</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>239012</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>300427</t>
+          <t>301551</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>417917</t>
+          <t>415547</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>470550</t>
+          <t>471396</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>456600</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>508176</t>
+          <t>509139</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>890806</t>
+          <t>887092</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>967780</t>
+          <t>963706</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7728</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6574</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7964</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3515</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4306</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3873</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13665</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10785</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29263</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3513</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11913</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12060</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>13378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35982</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47512</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>69,91%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>59,71%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>78,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>51530</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39079</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58936</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41535</t>
+          <t>36587</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101704</t>
+          <t>83798</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>86059</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112023</t>
+          <t>91069</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -1398,57 +1398,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3920</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4298</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5987</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6069</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12196</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10883</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17871</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11003</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4184</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17924</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50893</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40240</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62200</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>44,27%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>54,11%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29015</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13468</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>40839</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>32,5%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55381</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68716</t>
+          <t>36341</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>79347</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58727</t>
+          <t>64066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>93264</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50078</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39597</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>61274</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>78078</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61358</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>105241</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55545</t>
+          <t>52258</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43196</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>62130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>133622</t>
+          <t>102335</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>88436</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170383</t>
+          <t>118066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -2193,57 +2193,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,107 +2310,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3666</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7759</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3137</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6956</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13009</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>8385</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>18294</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>31,93%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7112</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3966</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>12133</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>10545</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>6731</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15341</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>27,61%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>31493</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>25136</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>37056</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>54,96%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>43,87%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>64,67%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>34106</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>28451</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>39640</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>61,4%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,36%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29093</t>
+          <t>27059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42888</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>70330</t>
+          <t>64192</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>56883</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78703</t>
+          <t>72500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -2988,57 +2988,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6899</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>9198</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2758</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>9631</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2856</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>939</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>63092</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>56329</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>67065</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>81,28%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>62942</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>57821</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>66272</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>83,97%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>69062</t>
+          <t>63471</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>61833</t>
+          <t>57675</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72753</t>
+          <t>66930</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>132004</t>
+          <t>126563</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>124174</t>
+          <t>118077</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>137421</t>
+          <t>132288</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -3783,57 +3783,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>69304</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>68857</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>68857</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>68857</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>74802</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>74802</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>74802</t>
+          <t>69588</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>138892</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>138892</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>143659</t>
+          <t>138892</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4126,107 +4126,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>3417</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3945</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>3856</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>16,29%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3994</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>27221</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>23032</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>31400</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>79,34%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>20152</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>15913</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>24243</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>70,89%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>31958</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>47666</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>9181</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>13831</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>14,59%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>34,94%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>8964</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>13015</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -4578,57 +4578,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,107 +4695,107 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2916</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4808,107 +4808,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2918</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>9725</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>4920</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>2257</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>9072</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>9699</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>18166</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>23622</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11952</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>7646</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>17132</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5147,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>8165</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>27,21%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>8787</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>5278</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>13556</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>14925</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>10456</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>20449</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>18087</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>13448</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>23849</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>40,84%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>53,85%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23750</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>33364</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -5373,57 +5373,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>474</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5603,107 +5603,107 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="Q47" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>4643</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>3509</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>7714</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>19735</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>13742</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>8911</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>21142</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>26751</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>37972</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -5947,17 +5947,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>39097</t>
+          <t>37401</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>107184</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>84008</t>
+          <t>97251</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>90502</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>108527</t>
+          <t>81617</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>128512</t>
+          <t>98522</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>211991</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>198819</t>
+          <t>184008</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>225253</t>
+          <t>209223</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -6168,57 +6168,57 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6511,72 +6511,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>4013</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -6624,107 +6624,107 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>5813</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>11277</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>10884</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>6354</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>18455</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
           <t>6,26%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>10555</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>18155</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -6737,72 +6737,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>24885</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>17673</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>34226</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>26639</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>18997</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>35398</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>50004</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -6850,72 +6850,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>126449</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>116673</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>134226</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>74,25%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>96053</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>86142</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>104329</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>74,65%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>124797</t>
+          <t>101518</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>115454</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>132474</t>
+          <t>111153</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>220849</t>
+          <t>227967</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>208450</t>
+          <t>213486</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>232568</t>
+          <t>241908</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -6963,57 +6963,57 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7193,107 +7193,107 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>7580</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>7825</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>30160</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -7419,72 +7419,72 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>72427</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>58950</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>85228</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>61570</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>48949</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>76236</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>61717</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>134144</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>117723</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>168418</t>
+          <t>154260</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7532,72 +7532,72 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>142618</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>162800</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>120549</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>102273</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>142856</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>117477</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>127036</t>
+          <t>101871</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>135764</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>269546</t>
+          <t>260095</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>238246</t>
+          <t>237508</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>301551</t>
+          <t>290234</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -7645,72 +7645,72 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>444531</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>422107</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>466943</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>442139</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>415547</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>471396</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>63,7%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>72,27%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>482179</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>456600</t>
+          <t>387816</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>509139</t>
+          <t>429729</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>924319</t>
+          <t>854553</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>887092</t>
+          <t>823894</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>963706</t>
+          <t>882122</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -7758,57 +7758,57 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
